--- a/data_processed/results_OLS_kWh_electricity_per_capitatenure.xlsx
+++ b/data_processed/results_OLS_kWh_electricity_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6855" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.7289" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3636.300006520315</v>
+        <v>3506.208039337944</v>
       </c>
       <c r="D2" t="n">
-        <v>5.519153989311707e-163</v>
+        <v>4.280486267436042e-170</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-153.5092359136024</v>
+        <v>-192.1394766215331</v>
       </c>
       <c r="D3" t="n">
-        <v>2.327650061477082e-41</v>
+        <v>1.14658721766865e-70</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-212.4131977417283</v>
+        <v>-246.1171689865358</v>
       </c>
       <c r="D4" t="n">
-        <v>1.320202945267943e-96</v>
+        <v>1.006707583695176e-141</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-47.3655854487687</v>
+        <v>-47.14715384620593</v>
       </c>
       <c r="D5" t="n">
-        <v>3.559845710574534e-25</v>
+        <v>7.89967970542624e-29</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38.30591204438845</v>
+        <v>34.67394066077815</v>
       </c>
       <c r="D6" t="n">
-        <v>1.216532812782778e-05</v>
+        <v>2.605069864862727e-05</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_train</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.0005557776540583084</v>
+        <v>-0.02661972184299778</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6820956956512886</v>
+        <v>0.000438418981535696</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1474028024772631</v>
+        <v>0.1377404139185169</v>
       </c>
       <c r="D8" t="n">
-        <v>2.141051294893847e-09</v>
+        <v>2.40980442739622e-09</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-926.3550424235639</v>
+        <v>-765.9082253045024</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7.721954804111291e-283</v>
       </c>
     </row>
     <row r="10">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.585208001334614</v>
+        <v>6.515305983297956</v>
       </c>
       <c r="D10" t="n">
-        <v>1.406759083006617e-06</v>
+        <v>9.188511001092288e-15</v>
       </c>
     </row>
     <row r="11">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>51.56940238602424</v>
+        <v>47.21257348978739</v>
       </c>
       <c r="D11" t="n">
-        <v>4.19586298305774e-48</v>
+        <v>3.346231230648211e-46</v>
       </c>
     </row>
     <row r="12">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-651.6104725011185</v>
+        <v>385.0900726386553</v>
       </c>
       <c r="D12" t="n">
-        <v>6.209908547145419e-08</v>
+        <v>0.003473845689022634</v>
       </c>
     </row>
     <row r="13">
@@ -627,14 +627,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>distance_depstore</t>
+          <t>solarcapacity</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.03762317118036593</v>
+        <v>-263.5060672684165</v>
       </c>
       <c r="D13" t="n">
-        <v>4.775557614044023e-06</v>
+        <v>7.188547570928539e-85</v>
       </c>
     </row>
   </sheetData>

--- a/data_processed/results_OLS_kWh_electricity_per_capitatenure.xlsx
+++ b/data_processed/results_OLS_kWh_electricity_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.7289" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6983" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3506.208039337944</v>
+        <v>3812.882475392766</v>
       </c>
       <c r="D2" t="n">
-        <v>4.280486267436042e-170</v>
+        <v>2.040496308398634e-185</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-192.1394766215331</v>
+        <v>-196.4431273682493</v>
       </c>
       <c r="D3" t="n">
-        <v>1.14658721766865e-70</v>
+        <v>7.468649606021583e-69</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-246.1171689865358</v>
+        <v>-813.6356163363698</v>
       </c>
       <c r="D4" t="n">
-        <v>1.006707583695176e-141</v>
+        <v>1.411615190883682e-297</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-47.14715384620593</v>
+        <v>5.440297022605594</v>
       </c>
       <c r="D5" t="n">
-        <v>7.89967970542624e-29</v>
+        <v>1.651423942305044e-09</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.67394066077815</v>
+        <v>-288.792378131077</v>
       </c>
       <c r="D6" t="n">
-        <v>2.605069864862727e-05</v>
+        <v>5.893904845886969e-184</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_depstore</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.02661972184299778</v>
+        <v>-52.81767168621173</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000438418981535696</v>
+        <v>5.319941800496574e-32</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1377404139185169</v>
+        <v>42.49379238382188</v>
       </c>
       <c r="D8" t="n">
-        <v>2.40980442739622e-09</v>
+        <v>1.819410119309813e-06</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-765.9082253045024</v>
+        <v>0.1234090176442353</v>
       </c>
       <c r="D9" t="n">
-        <v>7.721954804111291e-283</v>
+        <v>5.663287932473586e-07</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.515305983297956</v>
+        <v>-0.02203575799693653</v>
       </c>
       <c r="D10" t="n">
-        <v>9.188511001092288e-15</v>
+        <v>0.004594194358187021</v>
       </c>
     </row>
     <row r="11">
@@ -595,14 +595,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>heatpump_pc</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.21257348978739</v>
+        <v>295.5087595466182</v>
       </c>
       <c r="D11" t="n">
-        <v>3.346231230648211e-46</v>
+        <v>0.01993559381841091</v>
       </c>
     </row>
     <row r="12">
@@ -611,30 +611,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>heatpump_pc</t>
+          <t>solarcapacity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>385.0900726386553</v>
+        <v>-277.1968470279029</v>
       </c>
       <c r="D12" t="n">
-        <v>0.003473845689022634</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>solarcapacity</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-263.5060672684165</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.188547570928539e-85</v>
+        <v>1.039849209486552e-79</v>
       </c>
     </row>
   </sheetData>
